--- a/docs/descargas/fallecidos_sppat_2016_2021.xlsx
+++ b/docs/descargas/fallecidos_sppat_2016_2021.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R202c9b5ed78948e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="Rf94f434d26644a07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2016" sheetId="3" r:id="R834083ba02f64bdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2017" sheetId="4" r:id="R9e16547461a54672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2018" sheetId="5" r:id="R7612eca5a5e043e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2019" sheetId="6" r:id="Ra609a8097e4848d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="7" r:id="R73f8aff2cd1d45b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="8" r:id="Rcd8aa86d6cb14e37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="Rb03e54511cbb4c8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R3602c14d6c0e434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2016" sheetId="3" r:id="Rda178d04f4524e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2017" sheetId="4" r:id="R2867c07c7558403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2018" sheetId="5" r:id="R5465b2d55ad444bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2019" sheetId="6" r:id="R5ece2d6f64e7454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="7" r:id="Rad69e728b2d94f04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="8" r:id="R8ad9c1cb43f846b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -551,7 +551,7 @@
         <x:v>Producto</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Descarga pública del Catálogo de datos del Observatorio REDSA</x:v>
+        <x:v>Descarga pública del Catálogo de datos del Observatorio de Seguridad Vial y Movilidad Sostenible</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
